--- a/Employee_Reports_wi52/Marty Tolosa Ambas Q0229.xlsx
+++ b/Employee_Reports_wi52/Marty Tolosa Ambas Q0229.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-94</v>
+        <v>-102</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-83</v>
+        <v>-91</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-365</v>
+        <v>-373</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1216,11 +1216,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-440</v>
+        <v>-448</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-517</v>
+        <v>-525</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-366</v>
+        <v>-374</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1351,11 +1351,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-373</v>
+        <v>-381</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1437,11 +1437,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
